--- a/resources/templates/standard/B1100-05.xlsx
+++ b/resources/templates/standard/B1100-05.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>불량유출 봉쇄 작업표</t>
   </si>
@@ -746,10 +749,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -817,21 +822,21 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5" s="6"/>
       <c r="M5" s="5"/>
@@ -840,21 +845,21 @@
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6" s="9"/>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
       <c r="K6" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L6" s="9"/>
       <c r="M6" s="8"/>
@@ -863,7 +868,7 @@
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
@@ -916,7 +921,7 @@
     </row>
     <row r="10" ht="25.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -935,36 +940,36 @@
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
       <c r="E11" s="18"/>
       <c r="F11" s="19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11" s="19"/>
       <c r="H11" s="19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I11" s="19"/>
       <c r="J11" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K11" s="19"/>
       <c r="L11" s="19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M11" s="19"/>
       <c r="N11" s="19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O11" s="19"/>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -983,7 +988,7 @@
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
@@ -1002,7 +1007,7 @@
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
@@ -1021,7 +1026,7 @@
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
@@ -1040,7 +1045,7 @@
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
@@ -1059,7 +1064,7 @@
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" s="18"/>
       <c r="C17" s="18"/>
@@ -1078,7 +1083,7 @@
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" s="18"/>
       <c r="C18" s="18"/>
@@ -1097,7 +1102,7 @@
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" s="18"/>
       <c r="C19" s="18"/>
@@ -1116,7 +1121,7 @@
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
@@ -1152,7 +1157,7 @@
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" s="21"/>
       <c r="C22" s="21"/>
@@ -1196,7 +1201,7 @@
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
@@ -1215,7 +1220,7 @@
       <c r="G25" s="11"/>
       <c r="H25" s="11"/>
       <c r="I25" s="26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
@@ -1234,7 +1239,7 @@
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
@@ -1253,7 +1258,7 @@
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
       <c r="I27" s="26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J27" s="11"/>
       <c r="K27" s="11"/>
@@ -1272,7 +1277,7 @@
       <c r="G28" s="15"/>
       <c r="H28" s="15"/>
       <c r="I28" s="27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J28" s="15"/>
       <c r="K28" s="15"/>
